--- a/data/intermediate/desocupacion.xlsx
+++ b/data/intermediate/desocupacion.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="265">
   <si>
     <t>Indicador</t>
   </si>
@@ -806,6 +806,9 @@
   </si>
   <si>
     <t>2026/06</t>
+  </si>
+  <si>
+    <t>2026/07</t>
   </si>
 </sst>
 </file>
@@ -1137,7 +1140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D259"/>
+  <dimension ref="A1:D260"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1165,7 +1168,7 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>3.75273543478848</v>
+        <v>3.75274098735473</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1179,7 +1182,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>3.60126047247468</v>
+        <v>3.60126747525019</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1193,7 +1196,7 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>3.69942858623305</v>
+        <v>3.69943578274024</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1207,7 +1210,7 @@
         <v>9</v>
       </c>
       <c r="D5">
-        <v>3.61763242151352</v>
+        <v>3.61763939996425</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1221,7 +1224,7 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>3.83764114250763</v>
+        <v>3.8376446496527</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1235,7 +1238,7 @@
         <v>11</v>
       </c>
       <c r="D7">
-        <v>3.8342879834247</v>
+        <v>3.83429025149072</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1249,7 +1252,7 @@
         <v>12</v>
       </c>
       <c r="D8">
-        <v>3.65078820701704</v>
+        <v>3.65078621455053</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1263,7 +1266,7 @@
         <v>13</v>
       </c>
       <c r="D9">
-        <v>3.45339485596348</v>
+        <v>3.45338812258266</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1277,7 +1280,7 @@
         <v>14</v>
       </c>
       <c r="D10">
-        <v>3.45232400777327</v>
+        <v>3.45231180964984</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1291,7 +1294,7 @@
         <v>15</v>
       </c>
       <c r="D11">
-        <v>3.24245981573747</v>
+        <v>3.24245246666244</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1305,7 +1308,7 @@
         <v>16</v>
       </c>
       <c r="D12">
-        <v>3.02545072982209</v>
+        <v>3.02545049363661</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1319,7 +1322,7 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>3.10840485573826</v>
+        <v>3.10840520803906</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1333,7 +1336,7 @@
         <v>18</v>
       </c>
       <c r="D14">
-        <v>3.25445974415499</v>
+        <v>3.2544641097975</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1347,7 +1350,7 @@
         <v>19</v>
       </c>
       <c r="D15">
-        <v>3.53489037992812</v>
+        <v>3.53489697804119</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1361,7 +1364,7 @@
         <v>20</v>
       </c>
       <c r="D16">
-        <v>3.2932456832264</v>
+        <v>3.29325236651258</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1375,7 +1378,7 @@
         <v>21</v>
       </c>
       <c r="D17">
-        <v>3.41386997715208</v>
+        <v>3.41387781892459</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1389,7 +1392,7 @@
         <v>22</v>
       </c>
       <c r="D18">
-        <v>3.36741757826772</v>
+        <v>3.367421987684</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1403,7 +1406,7 @@
         <v>23</v>
       </c>
       <c r="D19">
-        <v>3.56053953085571</v>
+        <v>3.56053763736297</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1417,7 +1420,7 @@
         <v>24</v>
       </c>
       <c r="D20">
-        <v>3.6839699599017</v>
+        <v>3.68397082750906</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1431,7 +1434,7 @@
         <v>25</v>
       </c>
       <c r="D21">
-        <v>3.65165382497601</v>
+        <v>3.6516477612637</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1445,7 +1448,7 @@
         <v>26</v>
       </c>
       <c r="D22">
-        <v>3.65461133359244</v>
+        <v>3.6545970567744</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1459,7 +1462,7 @@
         <v>27</v>
       </c>
       <c r="D23">
-        <v>3.71690894522529</v>
+        <v>3.71689996640437</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1473,7 +1476,7 @@
         <v>28</v>
       </c>
       <c r="D24">
-        <v>3.79835918241889</v>
+        <v>3.79835799908395</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1487,7 +1490,7 @@
         <v>29</v>
       </c>
       <c r="D25">
-        <v>3.84499110540457</v>
+        <v>3.84499065328624</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1501,7 +1504,7 @@
         <v>30</v>
       </c>
       <c r="D26">
-        <v>3.72567396238681</v>
+        <v>3.72567772647121</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1515,7 +1518,7 @@
         <v>31</v>
       </c>
       <c r="D27">
-        <v>3.87975627733233</v>
+        <v>3.87976267385228</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1529,7 +1532,7 @@
         <v>32</v>
       </c>
       <c r="D28">
-        <v>3.85800059203625</v>
+        <v>3.8580090301278</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1543,7 +1546,7 @@
         <v>33</v>
       </c>
       <c r="D29">
-        <v>3.74776613627731</v>
+        <v>3.74777602228336</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1557,7 +1560,7 @@
         <v>34</v>
       </c>
       <c r="D30">
-        <v>3.60526109197666</v>
+        <v>3.60527172728224</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1571,7 +1574,7 @@
         <v>35</v>
       </c>
       <c r="D31">
-        <v>3.54137995532456</v>
+        <v>3.54137404279999</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1585,7 +1588,7 @@
         <v>36</v>
       </c>
       <c r="D32">
-        <v>3.50095352990697</v>
+        <v>3.50095705821667</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1599,7 +1602,7 @@
         <v>37</v>
       </c>
       <c r="D33">
-        <v>3.59783147000463</v>
+        <v>3.59782634315927</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1613,7 +1616,7 @@
         <v>38</v>
       </c>
       <c r="D34">
-        <v>3.51680146654643</v>
+        <v>3.51678620588138</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1627,7 +1630,7 @@
         <v>39</v>
       </c>
       <c r="D35">
-        <v>3.67939230562507</v>
+        <v>3.67938256313497</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1641,7 +1644,7 @@
         <v>40</v>
       </c>
       <c r="D36">
-        <v>3.51317132061408</v>
+        <v>3.51316912025946</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1655,7 +1658,7 @@
         <v>41</v>
       </c>
       <c r="D37">
-        <v>3.65839879942083</v>
+        <v>3.65839706017649</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1669,7 +1672,7 @@
         <v>42</v>
       </c>
       <c r="D38">
-        <v>3.88911922370028</v>
+        <v>3.88912190704447</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1683,7 +1686,7 @@
         <v>43</v>
       </c>
       <c r="D39">
-        <v>3.64387680341535</v>
+        <v>3.64388200299007</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1697,7 +1700,7 @@
         <v>44</v>
       </c>
       <c r="D40">
-        <v>3.69793143922537</v>
+        <v>3.69793997198267</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1711,7 +1714,7 @@
         <v>45</v>
       </c>
       <c r="D41">
-        <v>3.60025547515584</v>
+        <v>3.60026597286239</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1725,7 +1728,7 @@
         <v>46</v>
       </c>
       <c r="D42">
-        <v>3.64789272119912</v>
+        <v>3.64790889168214</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1739,7 +1742,7 @@
         <v>47</v>
       </c>
       <c r="D43">
-        <v>3.65452030334244</v>
+        <v>3.65450863686063</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1753,7 +1756,7 @@
         <v>48</v>
       </c>
       <c r="D44">
-        <v>3.84804009778441</v>
+        <v>3.84804682842995</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1767,7 +1770,7 @@
         <v>49</v>
       </c>
       <c r="D45">
-        <v>3.81136448181972</v>
+        <v>3.81136043598566</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1781,7 +1784,7 @@
         <v>50</v>
       </c>
       <c r="D46">
-        <v>3.8577273999376</v>
+        <v>3.85771095028303</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1795,7 +1798,7 @@
         <v>51</v>
       </c>
       <c r="D47">
-        <v>3.95893835522546</v>
+        <v>3.95892794982525</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1809,7 +1812,7 @@
         <v>52</v>
       </c>
       <c r="D48">
-        <v>4.6839563147386</v>
+        <v>4.6839518949133</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1823,7 +1826,7 @@
         <v>53</v>
       </c>
       <c r="D49">
-        <v>4.5089549836708</v>
+        <v>4.50895186002081</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1837,7 +1840,7 @@
         <v>54</v>
       </c>
       <c r="D50">
-        <v>4.65326489254749</v>
+        <v>4.65326632671013</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1851,7 +1854,7 @@
         <v>55</v>
       </c>
       <c r="D51">
-        <v>5.00356726502127</v>
+        <v>5.00357270421516</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1865,7 +1868,7 @@
         <v>56</v>
       </c>
       <c r="D52">
-        <v>5.04381362236919</v>
+        <v>5.04382477997313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1879,7 +1882,7 @@
         <v>57</v>
       </c>
       <c r="D53">
-        <v>5.3269194792459</v>
+        <v>5.3269340154928</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1893,7 +1896,7 @@
         <v>58</v>
       </c>
       <c r="D54">
-        <v>5.65566384769898</v>
+        <v>5.65569398671207</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1907,7 +1910,7 @@
         <v>59</v>
       </c>
       <c r="D55">
-        <v>5.45740097759258</v>
+        <v>5.45738230962503</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1921,7 +1924,7 @@
         <v>60</v>
       </c>
       <c r="D56">
-        <v>5.61687788136978</v>
+        <v>5.61688887723671</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1935,7 +1938,7 @@
         <v>61</v>
       </c>
       <c r="D57">
-        <v>5.74058389119952</v>
+        <v>5.74057926102987</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1949,7 +1952,7 @@
         <v>62</v>
       </c>
       <c r="D58">
-        <v>5.89699358410442</v>
+        <v>5.89696942384927</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1963,7 +1966,7 @@
         <v>63</v>
       </c>
       <c r="D59">
-        <v>5.59002761254228</v>
+        <v>5.59001494795668</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1977,7 +1980,7 @@
         <v>64</v>
       </c>
       <c r="D60">
-        <v>5.36072488408723</v>
+        <v>5.36071933386619</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1991,7 +1994,7 @@
         <v>65</v>
       </c>
       <c r="D61">
-        <v>5.26616509755225</v>
+        <v>5.2661610387739</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2005,7 +2008,7 @@
         <v>66</v>
       </c>
       <c r="D62">
-        <v>5.52311368942709</v>
+        <v>5.52311532285286</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2019,7 +2022,7 @@
         <v>67</v>
       </c>
       <c r="D63">
-        <v>5.2277820073618</v>
+        <v>5.22778755767246</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2033,7 +2036,7 @@
         <v>68</v>
       </c>
       <c r="D64">
-        <v>5.26842080747738</v>
+        <v>5.26843042007842</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2047,7 +2050,7 @@
         <v>69</v>
       </c>
       <c r="D65">
-        <v>5.46430616132852</v>
+        <v>5.46431948836607</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2061,7 +2064,7 @@
         <v>70</v>
       </c>
       <c r="D66">
-        <v>5.25824408565018</v>
+        <v>5.25826410206019</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2075,7 +2078,7 @@
         <v>71</v>
       </c>
       <c r="D67">
-        <v>5.19284827509997</v>
+        <v>5.19282869335962</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2089,7 +2092,7 @@
         <v>72</v>
       </c>
       <c r="D68">
-        <v>5.32351305685705</v>
+        <v>5.32352432749754</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2103,7 +2106,7 @@
         <v>73</v>
       </c>
       <c r="D69">
-        <v>4.97140288155746</v>
+        <v>4.9714016597369</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2117,7 +2120,7 @@
         <v>74</v>
       </c>
       <c r="D70">
-        <v>5.21386386187973</v>
+        <v>5.21384812874525</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2131,7 +2134,7 @@
         <v>75</v>
       </c>
       <c r="D71">
-        <v>5.4193343649395</v>
+        <v>5.41932665673969</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2145,7 +2148,7 @@
         <v>76</v>
       </c>
       <c r="D72">
-        <v>5.34624491101384</v>
+        <v>5.3462395407776</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2159,7 +2162,7 @@
         <v>77</v>
       </c>
       <c r="D73">
-        <v>5.47096123526836</v>
+        <v>5.4709582166567</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2173,7 +2176,7 @@
         <v>78</v>
       </c>
       <c r="D74">
-        <v>5.11060471165067</v>
+        <v>5.11060610333178</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2187,7 +2190,7 @@
         <v>79</v>
       </c>
       <c r="D75">
-        <v>5.28375755237521</v>
+        <v>5.28376198511845</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2201,7 +2204,7 @@
         <v>80</v>
       </c>
       <c r="D76">
-        <v>5.06011109607544</v>
+        <v>5.0601169305975</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2215,7 +2218,7 @@
         <v>81</v>
       </c>
       <c r="D77">
-        <v>5.17075434064231</v>
+        <v>5.17076273160348</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2229,7 +2232,7 @@
         <v>82</v>
       </c>
       <c r="D78">
-        <v>5.35226860294432</v>
+        <v>5.35227984793222</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2243,7 +2246,7 @@
         <v>83</v>
       </c>
       <c r="D79">
-        <v>5.57835232639449</v>
+        <v>5.5783367942483</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2257,7 +2260,7 @@
         <v>84</v>
       </c>
       <c r="D80">
-        <v>5.27353860326946</v>
+        <v>5.27354661850956</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2271,7 +2274,7 @@
         <v>85</v>
       </c>
       <c r="D81">
-        <v>5.34007531798192</v>
+        <v>5.34007549257905</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2285,7 +2288,7 @@
         <v>86</v>
       </c>
       <c r="D82">
-        <v>5.24011329919641</v>
+        <v>5.24010408078544</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2299,7 +2302,7 @@
         <v>87</v>
       </c>
       <c r="D83">
-        <v>4.8105530900304</v>
+        <v>4.81055074487528</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2313,7 +2316,7 @@
         <v>88</v>
       </c>
       <c r="D84">
-        <v>5.06131577202077</v>
+        <v>5.06131201687605</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2327,7 +2330,7 @@
         <v>89</v>
       </c>
       <c r="D85">
-        <v>5.02636619835125</v>
+        <v>5.0263650104752</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2341,7 +2344,7 @@
         <v>90</v>
       </c>
       <c r="D86">
-        <v>4.66886976753149</v>
+        <v>4.66887133975724</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2355,7 +2358,7 @@
         <v>91</v>
       </c>
       <c r="D87">
-        <v>5.42054546599605</v>
+        <v>5.42054885979114</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2369,7 +2372,7 @@
         <v>92</v>
       </c>
       <c r="D88">
-        <v>5.11603361998737</v>
+        <v>5.11603577477801</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2383,7 +2386,7 @@
         <v>93</v>
       </c>
       <c r="D89">
-        <v>4.89035528022497</v>
+        <v>4.89035903456987</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2397,7 +2400,7 @@
         <v>94</v>
       </c>
       <c r="D90">
-        <v>4.87708458052108</v>
+        <v>4.87708611207108</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2411,7 +2414,7 @@
         <v>95</v>
       </c>
       <c r="D91">
-        <v>4.85465427078282</v>
+        <v>4.85464497459012</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2425,7 +2428,7 @@
         <v>96</v>
       </c>
       <c r="D92">
-        <v>4.72327978509412</v>
+        <v>4.72328351003951</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2439,7 +2442,7 @@
         <v>97</v>
       </c>
       <c r="D93">
-        <v>4.93944625986569</v>
+        <v>4.93944702702817</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2453,7 +2456,7 @@
         <v>98</v>
       </c>
       <c r="D94">
-        <v>4.67138732733686</v>
+        <v>4.67138491947381</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2467,7 +2470,7 @@
         <v>99</v>
       </c>
       <c r="D95">
-        <v>4.83556157774391</v>
+        <v>4.83556262885307</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2481,7 +2484,7 @@
         <v>100</v>
       </c>
       <c r="D96">
-        <v>5.20582078567869</v>
+        <v>5.20582170133612</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2495,7 +2498,7 @@
         <v>101</v>
       </c>
       <c r="D97">
-        <v>4.97523775229401</v>
+        <v>4.97523956899459</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2509,7 +2512,7 @@
         <v>102</v>
       </c>
       <c r="D98">
-        <v>5.15671061329237</v>
+        <v>5.15671269197756</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2523,7 +2526,7 @@
         <v>103</v>
       </c>
       <c r="D99">
-        <v>4.95932749506811</v>
+        <v>4.95932873416326</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2537,7 +2540,7 @@
         <v>104</v>
       </c>
       <c r="D100">
-        <v>5.04990989093961</v>
+        <v>5.04990945488821</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2551,7 +2554,7 @@
         <v>105</v>
       </c>
       <c r="D101">
-        <v>5.11884154560843</v>
+        <v>5.1188334450853</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2565,7 +2568,7 @@
         <v>106</v>
       </c>
       <c r="D102">
-        <v>4.95861192519101</v>
+        <v>4.95861053743857</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2579,7 +2582,7 @@
         <v>107</v>
       </c>
       <c r="D103">
-        <v>5.07111542667903</v>
+        <v>5.07111315286547</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2593,7 +2596,7 @@
         <v>108</v>
       </c>
       <c r="D104">
-        <v>4.89568684130976</v>
+        <v>4.89568791118309</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2607,7 +2610,7 @@
         <v>109</v>
       </c>
       <c r="D105">
-        <v>4.82190450029047</v>
+        <v>4.82190488220422</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2621,7 +2624,7 @@
         <v>110</v>
       </c>
       <c r="D106">
-        <v>4.9841769388916</v>
+        <v>4.98417679222301</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2635,7 +2638,7 @@
         <v>111</v>
       </c>
       <c r="D107">
-        <v>4.88348008210033</v>
+        <v>4.88348284012327</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2649,7 +2652,7 @@
         <v>112</v>
       </c>
       <c r="D108">
-        <v>4.60935191375427</v>
+        <v>4.60935771830548</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2663,7 +2666,7 @@
         <v>113</v>
       </c>
       <c r="D109">
-        <v>4.79341432463084</v>
+        <v>4.79341685693988</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2677,7 +2680,7 @@
         <v>114</v>
       </c>
       <c r="D110">
-        <v>4.90642115198554</v>
+        <v>4.90642402039498</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2691,7 +2694,7 @@
         <v>115</v>
       </c>
       <c r="D111">
-        <v>4.81953950415659</v>
+        <v>4.81954140338734</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2705,7 +2708,7 @@
         <v>116</v>
       </c>
       <c r="D112">
-        <v>5.28594134411159</v>
+        <v>5.28594230037928</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2719,7 +2722,7 @@
         <v>117</v>
       </c>
       <c r="D113">
-        <v>4.91739646466615</v>
+        <v>4.91737670793116</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2733,7 +2736,7 @@
         <v>118</v>
       </c>
       <c r="D114">
-        <v>4.94211495945246</v>
+        <v>4.94211377977837</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2747,7 +2750,7 @@
         <v>119</v>
       </c>
       <c r="D115">
-        <v>4.82663371614283</v>
+        <v>4.82663057491388</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2761,7 +2764,7 @@
         <v>120</v>
       </c>
       <c r="D116">
-        <v>5.2163635867584</v>
+        <v>5.21636307942507</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2775,7 +2778,7 @@
         <v>121</v>
       </c>
       <c r="D117">
-        <v>4.84273587499395</v>
+        <v>4.84273609045094</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2789,7 +2792,7 @@
         <v>122</v>
       </c>
       <c r="D118">
-        <v>4.78401204473009</v>
+        <v>4.78401401109486</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2803,7 +2806,7 @@
         <v>123</v>
       </c>
       <c r="D119">
-        <v>4.64718252299363</v>
+        <v>4.64718711364353</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2817,7 +2820,7 @@
         <v>124</v>
       </c>
       <c r="D120">
-        <v>4.65555346754775</v>
+        <v>4.65556872938057</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2831,7 +2834,7 @@
         <v>125</v>
       </c>
       <c r="D121">
-        <v>4.16824123013459</v>
+        <v>4.16824513903326</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2845,7 +2848,7 @@
         <v>126</v>
       </c>
       <c r="D122">
-        <v>4.39203264001167</v>
+        <v>4.39203641425476</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2859,7 +2862,7 @@
         <v>127</v>
       </c>
       <c r="D123">
-        <v>4.44686599821347</v>
+        <v>4.44686871746378</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2873,7 +2876,7 @@
         <v>128</v>
       </c>
       <c r="D124">
-        <v>4.27550842994773</v>
+        <v>4.27550966761829</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2887,7 +2890,7 @@
         <v>129</v>
       </c>
       <c r="D125">
-        <v>4.34777967771473</v>
+        <v>4.3477473060649</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2901,7 +2904,7 @@
         <v>130</v>
       </c>
       <c r="D126">
-        <v>4.38547624206101</v>
+        <v>4.38547189253591</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2915,7 +2918,7 @@
         <v>131</v>
       </c>
       <c r="D127">
-        <v>4.41340478706331</v>
+        <v>4.41339768458819</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2929,7 +2932,7 @@
         <v>132</v>
       </c>
       <c r="D128">
-        <v>4.49114549520861</v>
+        <v>4.49114202320508</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2943,7 +2946,7 @@
         <v>133</v>
       </c>
       <c r="D129">
-        <v>4.38693772502287</v>
+        <v>4.38693785437763</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2957,7 +2960,7 @@
         <v>134</v>
       </c>
       <c r="D130">
-        <v>4.19566626899312</v>
+        <v>4.19567099159505</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2971,7 +2974,7 @@
         <v>135</v>
       </c>
       <c r="D131">
-        <v>4.44200624553145</v>
+        <v>4.44202716941849</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2985,7 +2988,7 @@
         <v>136</v>
       </c>
       <c r="D132">
-        <v>4.06421587983715</v>
+        <v>4.06423827509708</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2999,7 +3002,7 @@
         <v>137</v>
       </c>
       <c r="D133">
-        <v>4.30693230120488</v>
+        <v>4.30693989602427</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3013,7 +3016,7 @@
         <v>138</v>
       </c>
       <c r="D134">
-        <v>4.17176249792135</v>
+        <v>4.17176657357955</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3027,7 +3030,7 @@
         <v>139</v>
       </c>
       <c r="D135">
-        <v>4.25503202577529</v>
+        <v>4.25503272635195</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3041,7 +3044,7 @@
         <v>140</v>
       </c>
       <c r="D136">
-        <v>4.1438463660354</v>
+        <v>4.14384139815639</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3055,7 +3058,7 @@
         <v>141</v>
       </c>
       <c r="D137">
-        <v>3.82309356165871</v>
+        <v>3.82304952434844</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3069,7 +3072,7 @@
         <v>142</v>
       </c>
       <c r="D138">
-        <v>3.9539140452687</v>
+        <v>3.95390037797158</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3083,7 +3086,7 @@
         <v>143</v>
       </c>
       <c r="D139">
-        <v>3.92166882734174</v>
+        <v>3.92165290451502</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3097,7 +3100,7 @@
         <v>144</v>
       </c>
       <c r="D140">
-        <v>3.81147463240419</v>
+        <v>3.81146935797666</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3111,7 +3114,7 @@
         <v>145</v>
       </c>
       <c r="D141">
-        <v>3.7628251134959</v>
+        <v>3.76283065603769</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3125,7 +3128,7 @@
         <v>146</v>
       </c>
       <c r="D142">
-        <v>3.84417027404911</v>
+        <v>3.8441857175091</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3139,7 +3142,7 @@
         <v>147</v>
       </c>
       <c r="D143">
-        <v>3.58521786589151</v>
+        <v>3.58525633220967</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3153,7 +3156,7 @@
         <v>148</v>
       </c>
       <c r="D144">
-        <v>3.59397502215612</v>
+        <v>3.59400742641506</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3167,7 +3170,7 @@
         <v>149</v>
       </c>
       <c r="D145">
-        <v>3.63643848456831</v>
+        <v>3.63645786176441</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3181,7 +3184,7 @@
         <v>150</v>
       </c>
       <c r="D146">
-        <v>3.53533751649401</v>
+        <v>3.53535445433678</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3195,7 +3198,7 @@
         <v>151</v>
       </c>
       <c r="D147">
-        <v>3.46868338779313</v>
+        <v>3.46867533705111</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3209,7 +3212,7 @@
         <v>152</v>
       </c>
       <c r="D148">
-        <v>3.52682457357756</v>
+        <v>3.5268001466866</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3223,7 +3226,7 @@
         <v>153</v>
       </c>
       <c r="D149">
-        <v>3.47579811801656</v>
+        <v>3.475697662932</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3237,7 +3240,7 @@
         <v>154</v>
       </c>
       <c r="D150">
-        <v>3.50769824663364</v>
+        <v>3.50766276104298</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3251,7 +3254,7 @@
         <v>155</v>
       </c>
       <c r="D151">
-        <v>3.27687595589797</v>
+        <v>3.27683275927829</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3265,7 +3268,7 @@
         <v>156</v>
       </c>
       <c r="D152">
-        <v>3.25638841192164</v>
+        <v>3.25642110915226</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3279,7 +3282,7 @@
         <v>157</v>
       </c>
       <c r="D153">
-        <v>3.33334645314748</v>
+        <v>3.3333874173873</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3293,7 +3296,7 @@
         <v>158</v>
       </c>
       <c r="D154">
-        <v>3.34074834905969</v>
+        <v>3.340791074928</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3307,7 +3310,7 @@
         <v>159</v>
       </c>
       <c r="D155">
-        <v>3.44455422680859</v>
+        <v>3.44462252444163</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3321,7 +3324,7 @@
         <v>160</v>
       </c>
       <c r="D156">
-        <v>3.50010159708698</v>
+        <v>3.5001403235854</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3335,7 +3338,7 @@
         <v>161</v>
       </c>
       <c r="D157">
-        <v>3.39075380266553</v>
+        <v>3.39077844155928</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3349,7 +3352,7 @@
         <v>162</v>
       </c>
       <c r="D158">
-        <v>3.28170915308092</v>
+        <v>3.28171978806717</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3363,7 +3366,7 @@
         <v>163</v>
       </c>
       <c r="D159">
-        <v>3.29286299147447</v>
+        <v>3.29282521182776</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3377,7 +3380,7 @@
         <v>164</v>
       </c>
       <c r="D160">
-        <v>3.26541069454962</v>
+        <v>3.26535514794925</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3391,7 +3394,7 @@
         <v>165</v>
       </c>
       <c r="D161">
-        <v>3.38290116724454</v>
+        <v>3.38268448929942</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3405,7 +3408,7 @@
         <v>166</v>
       </c>
       <c r="D162">
-        <v>3.22405460838814</v>
+        <v>3.22402849951599</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3419,7 +3422,7 @@
         <v>167</v>
       </c>
       <c r="D163">
-        <v>3.35435982371345</v>
+        <v>3.35431267854089</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3433,7 +3436,7 @@
         <v>168</v>
       </c>
       <c r="D164">
-        <v>3.2934854701986</v>
+        <v>3.293587733062</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3447,7 +3450,7 @@
         <v>169</v>
       </c>
       <c r="D165">
-        <v>3.2688943267787</v>
+        <v>3.26898988753673</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3461,7 +3464,7 @@
         <v>170</v>
       </c>
       <c r="D166">
-        <v>3.33063556472603</v>
+        <v>3.33071372126254</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3475,7 +3478,7 @@
         <v>171</v>
       </c>
       <c r="D167">
-        <v>3.2016714757186</v>
+        <v>3.20175280162321</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3489,7 +3492,7 @@
         <v>172</v>
       </c>
       <c r="D168">
-        <v>3.34207652269216</v>
+        <v>3.34211846315724</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3503,7 +3506,7 @@
         <v>173</v>
       </c>
       <c r="D169">
-        <v>3.65994918425534</v>
+        <v>3.65994714677284</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3517,7 +3520,7 @@
         <v>174</v>
       </c>
       <c r="D170">
-        <v>3.45364316713902</v>
+        <v>3.45367533850548</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3531,7 +3534,7 @@
         <v>175</v>
       </c>
       <c r="D171">
-        <v>3.39215626038901</v>
+        <v>3.39205441091176</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3545,7 +3548,7 @@
         <v>176</v>
       </c>
       <c r="D172">
-        <v>3.6142836722017</v>
+        <v>3.61416294502438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3559,7 +3562,7 @@
         <v>177</v>
       </c>
       <c r="D173">
-        <v>3.48536825630711</v>
+        <v>3.48497801601094</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3573,7 +3576,7 @@
         <v>178</v>
       </c>
       <c r="D174">
-        <v>3.53900597397429</v>
+        <v>3.53901468486006</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3587,7 +3590,7 @@
         <v>179</v>
       </c>
       <c r="D175">
-        <v>3.53419516171885</v>
+        <v>3.53418237271309</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3601,7 +3604,7 @@
         <v>180</v>
       </c>
       <c r="D176">
-        <v>3.52505503535612</v>
+        <v>3.5252701443515</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3615,7 +3618,7 @@
         <v>181</v>
       </c>
       <c r="D177">
-        <v>3.48331371540519</v>
+        <v>3.48351652929041</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3629,7 +3632,7 @@
         <v>182</v>
       </c>
       <c r="D178">
-        <v>3.518264274801</v>
+        <v>3.51842545116206</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3643,7 +3646,7 @@
         <v>183</v>
       </c>
       <c r="D179">
-        <v>3.61489251907769</v>
+        <v>3.61498648042646</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3657,7 +3660,7 @@
         <v>184</v>
       </c>
       <c r="D180">
-        <v>3.53168710357099</v>
+        <v>3.53174037047553</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3671,7 +3674,7 @@
         <v>185</v>
       </c>
       <c r="D181">
-        <v>3.19659323310753</v>
+        <v>3.1966153720802</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3685,7 +3688,7 @@
         <v>186</v>
       </c>
       <c r="D182">
-        <v>3.64608127161707</v>
+        <v>3.64610291185083</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3699,7 +3702,7 @@
         <v>187</v>
       </c>
       <c r="D183">
-        <v>3.57233557790289</v>
+        <v>3.57171951667585</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3713,7 +3716,7 @@
         <v>188</v>
       </c>
       <c r="D184">
-        <v>3.32147880698199</v>
+        <v>3.3213926935189</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3727,7 +3730,7 @@
         <v>189</v>
       </c>
       <c r="D185">
-        <v>4.67418268019877</v>
+        <v>4.67335322695129</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3741,7 +3744,7 @@
         <v>190</v>
       </c>
       <c r="D186">
-        <v>4.28012180975406</v>
+        <v>4.28029055069905</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3755,7 +3758,7 @@
         <v>191</v>
       </c>
       <c r="D187">
-        <v>5.43978796625364</v>
+        <v>5.43949095828937</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3769,7 +3772,7 @@
         <v>192</v>
       </c>
       <c r="D188">
-        <v>5.01017253651051</v>
+        <v>5.01193704120022</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3783,7 +3786,7 @@
         <v>193</v>
       </c>
       <c r="D189">
-        <v>4.90189310060735</v>
+        <v>4.90204405596043</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3797,7 +3800,7 @@
         <v>194</v>
       </c>
       <c r="D190">
-        <v>4.79173132022585</v>
+        <v>4.79186941573413</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3811,7 +3814,7 @@
         <v>195</v>
       </c>
       <c r="D191">
-        <v>4.59059887017244</v>
+        <v>4.59060904052049</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3825,7 +3828,7 @@
         <v>196</v>
       </c>
       <c r="D192">
-        <v>4.51260567809274</v>
+        <v>4.51264509095928</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3839,7 +3842,7 @@
         <v>197</v>
       </c>
       <c r="D193">
-        <v>4.17167193291178</v>
+        <v>4.17169762773508</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3853,7 +3856,7 @@
         <v>198</v>
       </c>
       <c r="D194">
-        <v>4.53307245251723</v>
+        <v>4.53300794809994</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3867,7 +3870,7 @@
         <v>199</v>
       </c>
       <c r="D195">
-        <v>4.44169938210342</v>
+        <v>4.44036957649376</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3881,7 +3884,7 @@
         <v>200</v>
       </c>
       <c r="D196">
-        <v>4.46708930477147</v>
+        <v>4.46696718365421</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3895,7 +3898,7 @@
         <v>201</v>
       </c>
       <c r="D197">
-        <v>4.66856985737779</v>
+        <v>4.6673870415341</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3909,7 +3912,7 @@
         <v>202</v>
       </c>
       <c r="D198">
-        <v>4.076040927719</v>
+        <v>4.07597997367614</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3923,7 +3926,7 @@
         <v>203</v>
       </c>
       <c r="D199">
-        <v>3.97538584866194</v>
+        <v>3.9750170971926</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3937,7 +3940,7 @@
         <v>204</v>
       </c>
       <c r="D200">
-        <v>4.08428366578426</v>
+        <v>4.08703228031416</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3951,7 +3954,7 @@
         <v>205</v>
       </c>
       <c r="D201">
-        <v>3.99913939119778</v>
+        <v>3.99933815213982</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3965,7 +3968,7 @@
         <v>206</v>
       </c>
       <c r="D202">
-        <v>3.91810808709055</v>
+        <v>3.91832588349748</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3979,7 +3982,7 @@
         <v>207</v>
       </c>
       <c r="D203">
-        <v>3.85435657965278</v>
+        <v>3.8542873591629</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3993,7 +3996,7 @@
         <v>208</v>
       </c>
       <c r="D204">
-        <v>3.80359554091326</v>
+        <v>3.8036216092048</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4007,7 +4010,7 @@
         <v>209</v>
       </c>
       <c r="D205">
-        <v>3.81206149612197</v>
+        <v>3.81205058921155</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4021,7 +4024,7 @@
         <v>210</v>
       </c>
       <c r="D206">
-        <v>3.57590673547945</v>
+        <v>3.57559942270299</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4035,7 +4038,7 @@
         <v>211</v>
       </c>
       <c r="D207">
-        <v>3.81731269926505</v>
+        <v>3.81578603483986</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4049,7 +4052,7 @@
         <v>212</v>
       </c>
       <c r="D208">
-        <v>3.48171534899017</v>
+        <v>3.48139152230978</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4063,7 +4066,7 @@
         <v>213</v>
       </c>
       <c r="D209">
-        <v>3.06438802384077</v>
+        <v>3.06331431526683</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4077,7 +4080,7 @@
         <v>214</v>
       </c>
       <c r="D210">
-        <v>3.31855061090386</v>
+        <v>3.31820420961737</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4091,7 +4094,7 @@
         <v>215</v>
       </c>
       <c r="D211">
-        <v>3.30584497983025</v>
+        <v>3.30544293690987</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4105,7 +4108,7 @@
         <v>216</v>
       </c>
       <c r="D212">
-        <v>3.1920116371814</v>
+        <v>3.19524253892177</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4119,7 +4122,7 @@
         <v>217</v>
       </c>
       <c r="D213">
-        <v>3.23684036460037</v>
+        <v>3.23716072169702</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4133,7 +4136,7 @@
         <v>218</v>
       </c>
       <c r="D214">
-        <v>3.11419267954735</v>
+        <v>3.1145543955795</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4147,7 +4150,7 @@
         <v>219</v>
       </c>
       <c r="D215">
-        <v>3.23177854825079</v>
+        <v>3.2317622697658</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4161,7 +4164,7 @@
         <v>220</v>
       </c>
       <c r="D216">
-        <v>2.936386527</v>
+        <v>2.93642250175577</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4175,7 +4178,7 @@
         <v>221</v>
       </c>
       <c r="D217">
-        <v>2.96765534867639</v>
+        <v>2.9674934287869</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4189,7 +4192,7 @@
         <v>222</v>
       </c>
       <c r="D218">
-        <v>2.91085727144293</v>
+        <v>2.91036295560357</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4203,7 +4206,7 @@
         <v>223</v>
       </c>
       <c r="D219">
-        <v>2.83674169689339</v>
+        <v>2.83566825969801</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4217,7 +4220,7 @@
         <v>224</v>
       </c>
       <c r="D220">
-        <v>2.82525559094845</v>
+        <v>2.82432664428345</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4231,7 +4234,7 @@
         <v>225</v>
       </c>
       <c r="D221">
-        <v>2.87200684103409</v>
+        <v>2.87081042104138</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4245,7 +4248,7 @@
         <v>226</v>
       </c>
       <c r="D222">
-        <v>2.93087527595423</v>
+        <v>2.93007126145761</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4259,7 +4262,7 @@
         <v>227</v>
       </c>
       <c r="D223">
-        <v>2.60264982740429</v>
+        <v>2.60127609507297</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4273,7 +4276,7 @@
         <v>228</v>
       </c>
       <c r="D224">
-        <v>2.91006580737987</v>
+        <v>2.91543713958433</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4287,7 +4290,7 @@
         <v>229</v>
       </c>
       <c r="D225">
-        <v>2.68785789398809</v>
+        <v>2.68838103354138</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4301,7 +4304,7 @@
         <v>230</v>
       </c>
       <c r="D226">
-        <v>2.67275249624373</v>
+        <v>2.67318839731514</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4315,7 +4318,7 @@
         <v>231</v>
       </c>
       <c r="D227">
-        <v>2.70979768857602</v>
+        <v>2.70973673451639</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4329,7 +4332,7 @@
         <v>232</v>
       </c>
       <c r="D228">
-        <v>2.7817346845968</v>
+        <v>2.78176163064528</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4343,7 +4346,7 @@
         <v>233</v>
       </c>
       <c r="D229">
-        <v>2.80516399841704</v>
+        <v>2.80487240628731</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4357,7 +4360,7 @@
         <v>234</v>
       </c>
       <c r="D230">
-        <v>2.78166723398947</v>
+        <v>2.78101244714221</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4371,7 +4374,7 @@
         <v>235</v>
       </c>
       <c r="D231">
-        <v>2.59266169855056</v>
+        <v>2.59180831536665</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4385,7 +4388,7 @@
         <v>236</v>
       </c>
       <c r="D232">
-        <v>2.6916461102824</v>
+        <v>2.69008908645612</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4399,7 +4402,7 @@
         <v>237</v>
       </c>
       <c r="D233">
-        <v>2.67649133014654</v>
+        <v>2.6753458496793</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4413,7 +4416,7 @@
         <v>238</v>
       </c>
       <c r="D234">
-        <v>2.60269678760196</v>
+        <v>2.60093029075006</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4427,7 +4430,7 @@
         <v>239</v>
       </c>
       <c r="D235">
-        <v>2.70648480249649</v>
+        <v>2.70427579861622</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4441,7 +4444,7 @@
         <v>240</v>
       </c>
       <c r="D236">
-        <v>2.72101248559605</v>
+        <v>2.72773083221798</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4455,7 +4458,7 @@
         <v>241</v>
       </c>
       <c r="D237">
-        <v>2.7535249735352</v>
+        <v>2.75438524772642</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4469,7 +4472,7 @@
         <v>242</v>
       </c>
       <c r="D238">
-        <v>2.6987807924117</v>
+        <v>2.69939772556671</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4483,7 +4486,7 @@
         <v>243</v>
       </c>
       <c r="D239">
-        <v>2.48830469765987</v>
+        <v>2.48835043612316</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4497,7 +4500,7 @@
         <v>244</v>
       </c>
       <c r="D240">
-        <v>2.68606325625977</v>
+        <v>2.686177797383</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4511,7 +4514,7 @@
         <v>245</v>
       </c>
       <c r="D241">
-        <v>2.64388706904295</v>
+        <v>2.64361626838954</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4525,7 +4528,7 @@
         <v>246</v>
       </c>
       <c r="D242">
-        <v>2.64269420041277</v>
+        <v>2.64200040401168</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4539,7 +4542,7 @@
         <v>247</v>
       </c>
       <c r="D243">
-        <v>2.65773064280332</v>
+        <v>2.65667191016608</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4553,7 +4556,7 @@
         <v>248</v>
       </c>
       <c r="D244">
-        <v>2.60044548681303</v>
+        <v>2.59840094102973</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4567,7 +4570,7 @@
         <v>249</v>
       </c>
       <c r="D245">
-        <v>2.62216753711776</v>
+        <v>2.6210762056433</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4581,7 +4584,7 @@
         <v>250</v>
       </c>
       <c r="D246">
-        <v>2.70487525457611</v>
+        <v>2.70197788412321</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4595,7 +4598,7 @@
         <v>251</v>
       </c>
       <c r="D247">
-        <v>2.60425192535154</v>
+        <v>2.60129062158106</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4609,7 +4612,7 @@
         <v>252</v>
       </c>
       <c r="D248">
-        <v>2.58103074913713</v>
+        <v>2.58927831294602</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4623,7 +4626,7 @@
         <v>253</v>
       </c>
       <c r="D249">
-        <v>2.65519828255978</v>
+        <v>2.65635141925653</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4637,7 +4640,7 @@
         <v>254</v>
       </c>
       <c r="D250">
-        <v>2.7396430260395</v>
+        <v>2.74036319240487</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4651,7 +4654,7 @@
         <v>255</v>
       </c>
       <c r="D251">
-        <v>2.61816255901919</v>
+        <v>2.61820097613956</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4665,7 +4668,7 @@
         <v>256</v>
       </c>
       <c r="D252">
-        <v>2.70167188131323</v>
+        <v>2.70181866900535</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4679,7 +4682,7 @@
         <v>257</v>
       </c>
       <c r="D253">
-        <v>2.62798926854782</v>
+        <v>2.6277901183035</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4693,7 +4696,7 @@
         <v>258</v>
       </c>
       <c r="D254">
-        <v>2.64985847270039</v>
+        <v>2.64904126373665</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4707,7 +4710,7 @@
         <v>259</v>
       </c>
       <c r="D255">
-        <v>2.72496709291529</v>
+        <v>2.72355641049035</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4721,7 +4724,7 @@
         <v>260</v>
       </c>
       <c r="D256">
-        <v>2.80326703244806</v>
+        <v>2.80069814052351</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4735,7 +4738,7 @@
         <v>261</v>
       </c>
       <c r="D257">
-        <v>2.54890295853531</v>
+        <v>2.54771111104363</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4749,7 +4752,7 @@
         <v>262</v>
       </c>
       <c r="D258">
-        <v>2.72675504587019</v>
+        <v>2.72235139165539</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4763,7 +4766,21 @@
         <v>263</v>
       </c>
       <c r="D259">
-        <v>2.80397431213997</v>
+        <v>2.80067803287817</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" t="s">
+        <v>4</v>
+      </c>
+      <c r="B260" t="s">
+        <v>5</v>
+      </c>
+      <c r="C260" t="s">
+        <v>264</v>
+      </c>
+      <c r="D260">
+        <v>2.70934822064331</v>
       </c>
     </row>
   </sheetData>
